--- a/GHG_Calculation/output/income_level_emission_95PI.xlsx
+++ b/GHG_Calculation/output/income_level_emission_95PI.xlsx
@@ -622,100 +622,100 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>686.126598792267</v>
+        <v>680.1078636649776</v>
       </c>
       <c r="C2" t="n">
-        <v>662.3784185009933</v>
+        <v>657.0115391899667</v>
       </c>
       <c r="D2" t="n">
-        <v>685.1978512858011</v>
+        <v>679.3142704387624</v>
       </c>
       <c r="E2" t="n">
-        <v>715.7691708479229</v>
+        <v>707.1586981052527</v>
       </c>
       <c r="F2" t="n">
-        <v>157.373651508074</v>
+        <v>158.7101250318563</v>
       </c>
       <c r="G2" t="n">
-        <v>6.487608384914992</v>
+        <v>7.452864898263962</v>
       </c>
       <c r="H2" t="n">
-        <v>143.7015481845302</v>
+        <v>144.9168270568966</v>
       </c>
       <c r="I2" t="n">
-        <v>386.9280939802762</v>
+        <v>384.7034153843201</v>
       </c>
       <c r="J2" t="n">
-        <v>843.5002503003411</v>
+        <v>838.8179886968338</v>
       </c>
       <c r="K2" t="n">
-        <v>688.3708659435881</v>
+        <v>683.3050280530767</v>
       </c>
       <c r="L2" t="n">
-        <v>830.7052409295216</v>
+        <v>825.14000737984</v>
       </c>
       <c r="M2" t="n">
-        <v>1074.109106898818</v>
+        <v>1066.877956202938</v>
       </c>
       <c r="N2" t="n">
-        <v>78.79610716042085</v>
+        <v>78.60319941736921</v>
       </c>
       <c r="O2" t="n">
-        <v>74.7675543360954</v>
+        <v>74.58185093069402</v>
       </c>
       <c r="P2" t="n">
-        <v>78.74524560276768</v>
+        <v>78.5489240034162</v>
       </c>
       <c r="Q2" t="n">
-        <v>83.20761451298053</v>
+        <v>82.99674271017626</v>
       </c>
       <c r="R2" t="n">
-        <v>44285.8440129041</v>
+        <v>44106.75913575631</v>
       </c>
       <c r="S2" t="n">
-        <v>39845.32438764021</v>
+        <v>39656.28791188182</v>
       </c>
       <c r="T2" t="n">
-        <v>43962.90726965201</v>
+        <v>43773.98571891215</v>
       </c>
       <c r="U2" t="n">
-        <v>50572.32534285757</v>
+        <v>50388.89694238307</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02743921146927264</v>
+        <v>0.02719851340243493</v>
       </c>
       <c r="W2" t="n">
-        <v>0.026489486823457</v>
+        <v>0.02627485742910829</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02740206949099001</v>
+        <v>0.02716677644253127</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02862466150802642</v>
+        <v>0.02828031604342497</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03373281517305361</v>
+        <v>0.03354556464739372</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02752896301230717</v>
+        <v>0.02732637270697362</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.03322112393634129</v>
+        <v>0.03299856206435672</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.04295520240309392</v>
+        <v>0.04266601805510378</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.005323774170209047</v>
+        <v>0.005310740566180859</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.005051589334658703</v>
+        <v>0.005039042483949657</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.00532033776380969</v>
+        <v>0.005307073506255016</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.005621832916276664</v>
+        <v>0.005607585589886425</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.18956524021528</v>
+        <v>34.79679019655262</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69114051775389</v>
+        <v>20.63583270125847</v>
       </c>
       <c r="D3" t="n">
-        <v>31.73657917455718</v>
+        <v>31.4995350788363</v>
       </c>
       <c r="E3" t="n">
-        <v>72.92360105043238</v>
+        <v>72.92547095158696</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -761,76 +761,76 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>35.18956524021528</v>
+        <v>34.79679019655262</v>
       </c>
       <c r="K3" t="n">
-        <v>20.69114051775389</v>
+        <v>20.63583270125847</v>
       </c>
       <c r="L3" t="n">
-        <v>31.73657917455718</v>
+        <v>31.4995350788363</v>
       </c>
       <c r="M3" t="n">
-        <v>72.92360105043238</v>
+        <v>72.92547095158696</v>
       </c>
       <c r="N3" t="n">
-        <v>2.545425118501196</v>
+        <v>2.516332314434516</v>
       </c>
       <c r="O3" t="n">
-        <v>1.104380089261613</v>
+        <v>1.087934523232716</v>
       </c>
       <c r="P3" t="n">
-        <v>2.392944192751123</v>
+        <v>2.376870059675382</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.85222839353747</v>
+        <v>4.821081542338917</v>
       </c>
       <c r="R3" t="n">
-        <v>1645.019318836639</v>
+        <v>1626.472057147543</v>
       </c>
       <c r="S3" t="n">
-        <v>1063.499463699529</v>
+        <v>1059.481734689582</v>
       </c>
       <c r="T3" t="n">
-        <v>1574.690133963207</v>
+        <v>1556.324733236133</v>
       </c>
       <c r="U3" t="n">
-        <v>2666.486849065477</v>
+        <v>2671.294887382329</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04645568080589658</v>
+        <v>0.04593715686471239</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02731551279025827</v>
+        <v>0.0272424978992915</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04189720395634174</v>
+        <v>0.0415842690060927</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09627045717927452</v>
+        <v>0.09627292573864948</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.04645568080589658</v>
+        <v>0.04593715686471239</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02731551279025827</v>
+        <v>0.0272424978992915</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04189720395634174</v>
+        <v>0.0415842690060927</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.09627045717927452</v>
+        <v>0.09627292573864948</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.005067762970817995</v>
+        <v>0.005009841237393286</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.002198743338151767</v>
+        <v>0.002166001369059993</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.00476418413691096</v>
+        <v>0.004732181664790624</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.009660446579233879</v>
+        <v>0.00959843538196301</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -852,16 +852,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>418.6942789303993</v>
+        <v>413.5456942194876</v>
       </c>
       <c r="C4" t="n">
-        <v>329.6615881402839</v>
+        <v>325.6802213262873</v>
       </c>
       <c r="D4" t="n">
-        <v>400.5447102780846</v>
+        <v>394.5544801492858</v>
       </c>
       <c r="E4" t="n">
-        <v>643.2490792909663</v>
+        <v>624.12539793913</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -876,76 +876,76 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>418.6942789303993</v>
+        <v>413.5456942194876</v>
       </c>
       <c r="K4" t="n">
-        <v>329.6615881402839</v>
+        <v>325.6802213262873</v>
       </c>
       <c r="L4" t="n">
-        <v>400.5447102780846</v>
+        <v>394.5544801492858</v>
       </c>
       <c r="M4" t="n">
-        <v>643.2490792909663</v>
+        <v>624.12539793913</v>
       </c>
       <c r="N4" t="n">
-        <v>37.13146948846622</v>
+        <v>37.03366273591136</v>
       </c>
       <c r="O4" t="n">
-        <v>30.00624673090479</v>
+        <v>29.84595220423863</v>
       </c>
       <c r="P4" t="n">
-        <v>35.95411678621576</v>
+        <v>35.83277214377733</v>
       </c>
       <c r="Q4" t="n">
-        <v>51.11955792963536</v>
+        <v>51.40788149445174</v>
       </c>
       <c r="R4" t="n">
-        <v>21441.63670147206</v>
+        <v>21275.92367082996</v>
       </c>
       <c r="S4" t="n">
-        <v>18226.68228355576</v>
+        <v>18088.25830096101</v>
       </c>
       <c r="T4" t="n">
-        <v>21022.62177797389</v>
+        <v>20840.83459109979</v>
       </c>
       <c r="U4" t="n">
-        <v>27240.05503776269</v>
+        <v>27032.10165425308</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05959795126056094</v>
+        <v>0.05886508932261984</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04692482379423617</v>
+        <v>0.04635810646067921</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05701449798122757</v>
+        <v>0.05616183420906498</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09156162194028082</v>
+        <v>0.08883951111507248</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05959795126056094</v>
+        <v>0.05886508932261984</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04692482379423617</v>
+        <v>0.04635810646067921</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05701449798122757</v>
+        <v>0.05616183420906498</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.09156162194028082</v>
+        <v>0.08883951111507248</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005904250672760747</v>
+        <v>0.005888698485020049</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004771273663246763</v>
+        <v>0.004745785335422771</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00571704058977445</v>
+        <v>0.005697745657561344</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.008128487465087634</v>
+        <v>0.008174333606514076</v>
       </c>
       <c r="AH4" t="n">
         <v>1</v>
@@ -967,100 +967,100 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>654.0545544081349</v>
+        <v>646.6035405003017</v>
       </c>
       <c r="C5" t="n">
-        <v>602.1132956868871</v>
+        <v>596.370237756384</v>
       </c>
       <c r="D5" t="n">
-        <v>650.2838812456978</v>
+        <v>642.9397626802297</v>
       </c>
       <c r="E5" t="n">
-        <v>729.0518123120179</v>
+        <v>721.3374460987634</v>
       </c>
       <c r="F5" t="n">
-        <v>9.372299407413559</v>
+        <v>11.51463093660173</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3886674159663764</v>
+        <v>0.5385721034273971</v>
       </c>
       <c r="H5" t="n">
-        <v>8.591382931438094</v>
+        <v>10.53292932522566</v>
       </c>
       <c r="I5" t="n">
-        <v>22.93371047839313</v>
+        <v>28.08610443701281</v>
       </c>
       <c r="J5" t="n">
-        <v>663.4268538155485</v>
+        <v>658.1181714369035</v>
       </c>
       <c r="K5" t="n">
-        <v>610.1454976613104</v>
+        <v>605.0606368738883</v>
       </c>
       <c r="L5" t="n">
-        <v>659.9109640307174</v>
+        <v>654.7863557166543</v>
       </c>
       <c r="M5" t="n">
-        <v>739.8291314743464</v>
+        <v>734.5012868878846</v>
       </c>
       <c r="N5" t="n">
-        <v>119.2545434222021</v>
+        <v>119.5648098086799</v>
       </c>
       <c r="O5" t="n">
-        <v>109.9622264997169</v>
+        <v>110.4682429763128</v>
       </c>
       <c r="P5" t="n">
-        <v>119.0333796451972</v>
+        <v>119.2627584801085</v>
       </c>
       <c r="Q5" t="n">
-        <v>129.9104211722083</v>
+        <v>130.6278479005156</v>
       </c>
       <c r="R5" t="n">
-        <v>50469.01540728102</v>
+        <v>50410.38370656602</v>
       </c>
       <c r="S5" t="n">
-        <v>47643.30544825445</v>
+        <v>47559.4940803044</v>
       </c>
       <c r="T5" t="n">
-        <v>50422.10471570837</v>
+        <v>50327.04868402531</v>
       </c>
       <c r="U5" t="n">
-        <v>53684.13293130186</v>
+        <v>53631.56190104412</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03145781133007759</v>
+        <v>0.03109944276869282</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02895961250845428</v>
+        <v>0.02868339085138018</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03127645470755751</v>
+        <v>0.03092322745050205</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03506492571145889</v>
+        <v>0.03469389079513254</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03190858722407654</v>
+        <v>0.03165325756150757</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02934593424962025</v>
+        <v>0.02910136964837658</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03173948482005973</v>
+        <v>0.03149300849725478</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03558327830233619</v>
+        <v>0.03532702700239905</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005916538392343846</v>
+        <v>0.005931931541609029</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.00545552157698388</v>
+        <v>0.005480626414292583</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.005905565862995317</v>
+        <v>0.005916945963444312</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.006445205124887779</v>
+        <v>0.00648079859294288</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
